--- a/docs/workbook-split/dateien/Steuerung.xlsx
+++ b/docs/workbook-split/dateien/Steuerung.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red]\(#,##0.00\);&quot;–&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\);&quot;–&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -117,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -138,13 +137,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -639,7 +644,7 @@
       <c r="D7" s="1" t="n"/>
       <c r="E7" s="1" t="n"/>
       <c r="F7" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -657,9 +662,8 @@
       </c>
       <c r="D8" s="1" t="n"/>
       <c r="E8" s="1" t="n"/>
-      <c r="F8" s="1">
-        <f>'[D Finanzen.xlsx]D Finanzen'!B39</f>
-        <v/>
+      <c r="F8" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -738,7 +742,7 @@
       </c>
       <c r="D12" s="1" t="n"/>
       <c r="E12" s="1" t="n"/>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -1069,7 +1073,7 @@
       </c>
       <c r="D36" s="1" t="n"/>
       <c r="E36" s="1" t="n"/>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="12" t="n">
         <v>119</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="1" t="n"/>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="12" t="n">
         <v>45</v>
       </c>
       <c r="G37" s="1" t="inlineStr">
@@ -1117,7 +1121,7 @@
       </c>
       <c r="D38" s="1" t="n"/>
       <c r="E38" s="1" t="n"/>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="12" t="n">
         <v>209759.08</v>
       </c>
       <c r="G38" s="1" t="inlineStr">
@@ -1141,7 +1145,7 @@
       </c>
       <c r="D39" s="1" t="n"/>
       <c r="E39" s="1" t="n"/>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="1" t="inlineStr">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="D40" s="1" t="n"/>
       <c r="E40" s="1" t="n"/>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="12" t="n">
         <v>30.4375</v>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -1189,7 +1193,7 @@
       </c>
       <c r="D41" s="1" t="n"/>
       <c r="E41" s="1" t="n"/>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="12" t="n">
         <v>333887.39</v>
       </c>
       <c r="G41" s="1" t="inlineStr">
@@ -1213,7 +1217,7 @@
       </c>
       <c r="D42" s="1" t="n"/>
       <c r="E42" s="1" t="n"/>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="12" t="n">
         <v>9455.99</v>
       </c>
       <c r="G42" s="1" t="inlineStr">
@@ -1237,7 +1241,7 @@
       </c>
       <c r="D43" s="1" t="n"/>
       <c r="E43" s="1" t="n"/>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="12" t="n">
         <v>4058.81</v>
       </c>
       <c r="G43" s="1" t="inlineStr">
@@ -1261,7 +1265,7 @@
       </c>
       <c r="D44" s="1" t="n"/>
       <c r="E44" s="1" t="n"/>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="12" t="n">
         <v>1476386.65</v>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="D45" s="1" t="n"/>
       <c r="E45" s="1" t="n"/>
-      <c r="F45" s="10" t="n">
+      <c r="F45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="1" t="inlineStr">
@@ -1309,7 +1313,7 @@
       </c>
       <c r="D46" s="1" t="n"/>
       <c r="E46" s="1" t="n"/>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="D47" s="1" t="n"/>
       <c r="E47" s="1" t="n"/>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -1357,7 +1361,7 @@
       </c>
       <c r="D48" s="1" t="n"/>
       <c r="E48" s="1" t="n"/>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="12" t="n">
         <v>0.19</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="D49" s="1" t="n"/>
       <c r="E49" s="1" t="n"/>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G49" s="1" t="inlineStr">
@@ -1405,7 +1409,7 @@
       </c>
       <c r="D50" s="1" t="n"/>
       <c r="E50" s="1" t="n"/>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G50" s="1" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="D51" s="1" t="n"/>
       <c r="E51" s="1" t="n"/>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="12" t="n">
         <v>1944327.5</v>
       </c>
       <c r="G51" s="1" t="inlineStr">
@@ -1587,6 +1591,8 @@
       <c r="M60" s="1" t="n"/>
       <c r="N60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>

--- a/docs/workbook-split/dateien/Steuerung.xlsx
+++ b/docs/workbook-split/dateien/Steuerung.xlsx
@@ -1591,8 +1591,6 @@
       <c r="M60" s="1" t="n"/>
       <c r="N60" s="1" t="n"/>
     </row>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
